--- a/Assets/Data/Dungeon3010.xlsx
+++ b/Assets/Data/Dungeon3010.xlsx
@@ -68,10 +68,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -97,16 +97,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -127,11 +127,79 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -143,34 +211,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -187,51 +232,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -242,7 +242,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -254,19 +272,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -278,13 +296,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -296,97 +404,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,31 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -433,30 +433,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -479,16 +455,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -504,6 +471,32 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -525,11 +518,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -541,19 +541,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -562,124 +562,124 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Dungeon3010.xlsx
+++ b/Assets/Data/Dungeon3010.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -99,10 +99,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -121,23 +121,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -151,8 +135,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -167,37 +173,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -213,15 +205,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,8 +218,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,17 +235,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -273,7 +273,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -285,7 +339,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -297,7 +417,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -309,145 +435,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,6 +467,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -477,16 +492,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -506,21 +521,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -533,16 +533,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -572,145 +572,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -733,12 +733,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -826,169 +826,185 @@
         </row>
         <row r="4">
           <cell r="D4">
-            <v>2010</v>
+            <v>1020</v>
           </cell>
           <cell r="E4" t="str">
-            <v>ダンジョンから出る</v>
+            <v>エンフェリアイベント再生</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2020</v>
+            <v>2010</v>
           </cell>
           <cell r="E5" t="str">
-            <v>ダンジョン移動</v>
+            <v>ダンジョンから出る</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6">
-            <v>2021</v>
+            <v>2011</v>
           </cell>
           <cell r="E6" t="str">
-            <v>移動判定なしでダンジョン移動</v>
+            <v>ダンジョンから出る（確認無し）</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7">
-            <v>2030</v>
+            <v>2020</v>
           </cell>
           <cell r="E7" t="str">
-            <v>ダンジョンクリア</v>
+            <v>ダンジョン移動</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>3010</v>
+            <v>2021</v>
           </cell>
           <cell r="E8" t="str">
-            <v>アーティファクト取得</v>
+            <v>移動判定なしでダンジョン移動</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>3020</v>
+            <v>2030</v>
           </cell>
           <cell r="E9" t="str">
-            <v>アイテム取得</v>
+            <v>ダンジョンクリア</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>3030</v>
+            <v>3010</v>
           </cell>
           <cell r="E10" t="str">
-            <v>魔法入手</v>
+            <v>アーティファクト取得</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>4010</v>
+            <v>3020</v>
           </cell>
           <cell r="E11" t="str">
-            <v>仲間を増やす</v>
+            <v>アイテム取得</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12">
-            <v>4011</v>
+            <v>3030</v>
           </cell>
           <cell r="E12" t="str">
-            <v>仲間を外す</v>
+            <v>魔法入手</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13">
-            <v>4020</v>
+            <v>4010</v>
           </cell>
           <cell r="E13" t="str">
-            <v>選択して仲間を増やす</v>
+            <v>仲間を増やす</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14">
-            <v>5010</v>
+            <v>4011</v>
           </cell>
           <cell r="E14" t="str">
-            <v>強制戦闘</v>
+            <v>仲間を外す</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15">
-            <v>5020</v>
+            <v>4020</v>
           </cell>
           <cell r="E15" t="str">
-            <v>強制ボス戦闘</v>
+            <v>選択して仲間を増やす</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16">
-            <v>6010</v>
+            <v>5010</v>
           </cell>
           <cell r="E16" t="str">
-            <v>指定のイベントマスを消す</v>
+            <v>強制戦闘</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>6011</v>
+            <v>5020</v>
           </cell>
           <cell r="E17" t="str">
-            <v>指定のイベントマスを表示する</v>
+            <v>強制ボス戦闘</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18">
-            <v>6020</v>
+            <v>6010</v>
           </cell>
           <cell r="E18" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+            <v>指定のイベントマスを消す</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19">
-            <v>6030</v>
+            <v>6011</v>
           </cell>
           <cell r="E19" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
+            <v>指定のイベントマスを表示する</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>7010</v>
+            <v>6020</v>
           </cell>
           <cell r="E20" t="str">
-            <v>ダメージ床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>7020</v>
+            <v>6030</v>
           </cell>
           <cell r="E21" t="str">
-            <v>怨嗟床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22">
-            <v>7021</v>
+            <v>7010</v>
           </cell>
           <cell r="E22" t="str">
-            <v>怨嗟床解除</v>
+            <v>ダメージ床</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23">
-            <v>8010</v>
+            <v>7020</v>
           </cell>
           <cell r="E23" t="str">
-            <v>指定リージョンを開示する</v>
+            <v>怨嗟床</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24">
+            <v>7021</v>
+          </cell>
+          <cell r="E24" t="str">
+            <v>怨嗟床解除</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="D25">
+            <v>8010</v>
+          </cell>
+          <cell r="E25" t="str">
+            <v>指定リージョンを開示する</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="D26">
             <v>9010</v>
           </cell>
-          <cell r="E24" t="str">
+          <cell r="E26" t="str">
             <v>イベント終了明示</v>
           </cell>
         </row>
@@ -5602,8 +5618,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
+  <cols>
+    <col min="7" max="7" width="24.6363636363636" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
@@ -5727,7 +5746,7 @@
         <v>仲間を増やす</v>
       </c>
       <c r="H4">
-        <v>102</v>
+        <v>201</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -5747,26 +5766,26 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>3010</v>
       </c>
       <c r="F5">
-        <v>4010</v>
+        <v>5010</v>
       </c>
       <c r="G5" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F5,[1]Define!D:D))</f>
-        <v>仲間を増やす</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H5">
-        <v>103</v>
+        <v>1010</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -5783,17 +5802,17 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>3010</v>
+        <v>3030</v>
       </c>
       <c r="F6">
-        <v>5010</v>
+        <v>1010</v>
       </c>
       <c r="G6" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F6,[1]Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>Adv再生</v>
       </c>
       <c r="H6">
-        <v>1010</v>
+        <v>30020</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5813,10 +5832,10 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="F7">
         <v>1010</v>
@@ -5826,7 +5845,7 @@
         <v>Adv再生</v>
       </c>
       <c r="H7">
-        <v>30020</v>
+        <v>141</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5852,14 +5871,14 @@
         <v>3010</v>
       </c>
       <c r="F8">
-        <v>1010</v>
+        <v>6010</v>
       </c>
       <c r="G8" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F8,[1]Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H8">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5879,17 +5898,13 @@
         <v>9</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>3010</v>
       </c>
       <c r="F9">
-        <v>6010</v>
-      </c>
-      <c r="G9" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F9,[1]Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>93</v>
@@ -5912,16 +5927,20 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D10">
         <v>3010</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1010</v>
+      </c>
+      <c r="G10" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F10,[1]Define!D:D))</f>
+        <v>Adv再生</v>
       </c>
       <c r="H10">
-        <v>93</v>
+        <v>30030</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -5930,72 +5949,6 @@
         <v>0</v>
       </c>
       <c r="K10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11">
-        <v>3010</v>
-      </c>
-      <c r="B11">
-        <v>9</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <v>3010</v>
-      </c>
-      <c r="F11">
-        <v>1010</v>
-      </c>
-      <c r="G11" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F11,[1]Define!D:D))</f>
-        <v>Adv再生</v>
-      </c>
-      <c r="H11">
-        <v>30030</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12">
-        <v>3010</v>
-      </c>
-      <c r="B12">
-        <v>9</v>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12">
-        <v>3010</v>
-      </c>
-      <c r="F12">
-        <v>4011</v>
-      </c>
-      <c r="G12" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F12,[1]Define!D:D))</f>
-        <v>仲間を外す</v>
-      </c>
-      <c r="H12">
-        <v>103</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/Dungeon3010.xlsx
+++ b/Assets/Data/Dungeon3010.xlsx
@@ -99,10 +99,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -121,75 +121,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -203,24 +142,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,7 +158,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,6 +180,29 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -258,7 +211,54 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,7 +273,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -285,25 +417,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -315,145 +447,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,6 +464,17 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -478,15 +489,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -506,28 +508,29 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -547,20 +550,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -572,7 +572,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -581,136 +581,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Dungeon3010.xlsx
+++ b/Assets/Data/Dungeon3010.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -99,10 +99,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -120,6 +120,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -128,7 +158,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -143,14 +181,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -158,24 +188,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -187,16 +202,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -210,8 +218,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,15 +236,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,17 +257,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,13 +273,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -291,25 +291,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -321,13 +321,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -339,13 +375,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -357,31 +387,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,13 +411,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,25 +423,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,7 +441,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,17 +464,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -489,6 +478,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -510,9 +514,20 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -529,23 +544,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -572,7 +572,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -581,136 +581,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -834,177 +834,185 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2010</v>
+            <v>1030</v>
           </cell>
           <cell r="E5" t="str">
-            <v>ダンジョンから出る</v>
+            <v>メインイベント再生</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6">
-            <v>2011</v>
+            <v>2010</v>
           </cell>
           <cell r="E6" t="str">
-            <v>ダンジョンから出る（確認無し）</v>
+            <v>ダンジョンから出る</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7">
-            <v>2020</v>
+            <v>2011</v>
           </cell>
           <cell r="E7" t="str">
-            <v>ダンジョン移動</v>
+            <v>ダンジョンから出る（確認無し）</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>2021</v>
+            <v>2020</v>
           </cell>
           <cell r="E8" t="str">
-            <v>移動判定なしでダンジョン移動</v>
+            <v>ダンジョン移動</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>2030</v>
+            <v>2021</v>
           </cell>
           <cell r="E9" t="str">
-            <v>ダンジョンクリア</v>
+            <v>移動判定なしでダンジョン移動</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>3010</v>
+            <v>2030</v>
           </cell>
           <cell r="E10" t="str">
-            <v>アーティファクト取得</v>
+            <v>ダンジョンクリア</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>3020</v>
+            <v>3010</v>
           </cell>
           <cell r="E11" t="str">
-            <v>アイテム取得</v>
+            <v>アーティファクト取得</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12">
-            <v>3030</v>
+            <v>3020</v>
           </cell>
           <cell r="E12" t="str">
-            <v>魔法入手</v>
+            <v>アイテム取得</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13">
-            <v>4010</v>
+            <v>3030</v>
           </cell>
           <cell r="E13" t="str">
-            <v>仲間を増やす</v>
+            <v>魔法入手</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14">
-            <v>4011</v>
+            <v>4010</v>
           </cell>
           <cell r="E14" t="str">
-            <v>仲間を外す</v>
+            <v>仲間を増やす</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15">
-            <v>4020</v>
+            <v>4011</v>
           </cell>
           <cell r="E15" t="str">
-            <v>選択して仲間を増やす</v>
+            <v>仲間を外す</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16">
-            <v>5010</v>
+            <v>4020</v>
           </cell>
           <cell r="E16" t="str">
-            <v>強制戦闘</v>
+            <v>選択して仲間を増やす</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>5020</v>
+            <v>5010</v>
           </cell>
           <cell r="E17" t="str">
-            <v>強制ボス戦闘</v>
+            <v>強制戦闘</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18">
-            <v>6010</v>
+            <v>5020</v>
           </cell>
           <cell r="E18" t="str">
-            <v>指定のイベントマスを消す</v>
+            <v>強制ボス戦闘</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19">
-            <v>6011</v>
+            <v>6010</v>
           </cell>
           <cell r="E19" t="str">
-            <v>指定のイベントマスを表示する</v>
+            <v>指定のイベントマスを消す</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>6020</v>
+            <v>6011</v>
           </cell>
           <cell r="E20" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+            <v>指定のイベントマスを表示する</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>6030</v>
+            <v>6020</v>
           </cell>
           <cell r="E21" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22">
-            <v>7010</v>
+            <v>6030</v>
           </cell>
           <cell r="E22" t="str">
-            <v>ダメージ床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23">
-            <v>7020</v>
+            <v>7010</v>
           </cell>
           <cell r="E23" t="str">
-            <v>怨嗟床</v>
+            <v>ダメージ床</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24">
-            <v>7021</v>
+            <v>7020</v>
           </cell>
           <cell r="E24" t="str">
-            <v>怨嗟床解除</v>
+            <v>怨嗟床</v>
           </cell>
         </row>
         <row r="25">
           <cell r="D25">
-            <v>8010</v>
+            <v>7021</v>
           </cell>
           <cell r="E25" t="str">
-            <v>指定リージョンを開示する</v>
+            <v>怨嗟床解除</v>
           </cell>
         </row>
         <row r="26">
           <cell r="D26">
+            <v>8010</v>
+          </cell>
+          <cell r="E26" t="str">
+            <v>指定リージョンを開示する</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="D27">
             <v>9010</v>
           </cell>
-          <cell r="E26" t="str">
+          <cell r="E27" t="str">
             <v>イベント終了明示</v>
           </cell>
         </row>
